--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71D0DE2A-3306-451D-953D-EB295C93907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA27F19-F43B-4EB5-A366-414B10FF0894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -84,13 +84,19 @@
   </si>
   <si>
     <t>VITÓRIA GABRIELLI GODOY DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,19 +107,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,13 +120,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8D0D2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEE3E6"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -142,42 +134,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFFFFFFF"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -510,171 +494,332 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E4E142-EB18-47C9-8CD6-5BE4D1390D4A}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.6328125" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2">
+        <v>46254</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1">
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1">
+      <c r="C15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl02$lnkAnotacoes','')" xr:uid="{A7E52AFD-D53D-440F-8AD9-5ADE5DC19ADB}"/>
-    <hyperlink ref="C2" r:id="rId2" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl03$lnkAnotacoes','')" xr:uid="{B8A4E930-BFCF-491E-8BEB-2C7CCD16767F}"/>
-    <hyperlink ref="C3" r:id="rId3" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl04$lnkAnotacoes','')" xr:uid="{EDE569A6-06AE-433A-8F80-80686A02F7C4}"/>
-    <hyperlink ref="C4" r:id="rId4" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl05$lnkAnotacoes','')" xr:uid="{9AD61AF8-B5B8-4951-AF61-5379992AB83C}"/>
-    <hyperlink ref="C5" r:id="rId5" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl06$lnkAnotacoes','')" xr:uid="{CC0BEF73-4CB9-49E3-9351-D576A40A323E}"/>
-    <hyperlink ref="C6" r:id="rId6" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl07$lnkAnotacoes','')" xr:uid="{DBFF4BFE-9F08-4893-BABF-42AC3C1ECC7C}"/>
-    <hyperlink ref="C7" r:id="rId7" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl08$lnkAnotacoes','')" xr:uid="{BE9ED547-8012-4EC0-82B5-099B9E712DB6}"/>
-    <hyperlink ref="C8" r:id="rId8" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl09$lnkAnotacoes','')" xr:uid="{20D90B39-C41C-430B-ABDB-1176B32941B3}"/>
-    <hyperlink ref="C9" r:id="rId9" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl10$lnkAnotacoes','')" xr:uid="{83ECF75F-779E-475B-B9C0-9CEEBA51562D}"/>
-    <hyperlink ref="C10" r:id="rId10" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl11$lnkAnotacoes','')" xr:uid="{FB17F4D0-E1AB-47FA-9899-063E654F28D0}"/>
-    <hyperlink ref="C11" r:id="rId11" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl12$lnkAnotacoes','')" xr:uid="{BAF278FA-16DE-40D4-800E-BEABA8413CDC}"/>
-    <hyperlink ref="C12" r:id="rId12" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl13$lnkAnotacoes','')" xr:uid="{57520154-1ACE-4452-9E44-DA72FCBA8784}"/>
-    <hyperlink ref="C13" r:id="rId13" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl14$lnkAnotacoes','')" xr:uid="{ED771D15-4B6D-4A26-A6D6-9C253CAA8D57}"/>
-    <hyperlink ref="C14" r:id="rId14" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl15$lnkAnotacoes','')" xr:uid="{82FC2FA3-34F8-40C7-962D-6AD8A22C7E7C}"/>
-    <hyperlink ref="C15" r:id="rId15" tooltip="Anotações do Aluno" display="javascript:__doPostBack('ctl00$MainContent$gdv$ctl16$lnkAnotacoes','')" xr:uid="{C112490A-7F61-49E2-A1B2-12C72859698D}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010093213D9F94826D42BC9EF0DBA8180378" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="af650f022ad4c56918cd59f318082a35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5961bfb0-077a-48f3-b3a8-28880a00c350" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c862f0df734372448ddd1e114a488d17" ns3:_="">
     <xsd:import namespace="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
@@ -854,24 +999,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -887,28 +1039,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA27F19-F43B-4EB5-A366-414B10FF0894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6871CE-DE58-4E2D-A2A7-557E07CA50AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -564,7 +564,9 @@
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -598,7 +600,9 @@
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -615,7 +619,9 @@
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -632,7 +638,9 @@
       <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -685,7 +693,9 @@
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -803,20 +813,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,6 +1010,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1011,14 +1029,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6871CE-DE58-4E2D-A2A7-557E07CA50AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92C6CD4-DAED-4503-8165-41763902D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -510,7 +510,9 @@
       <c r="C1" s="2">
         <v>46254</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2">
+        <v>46275</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -529,7 +531,9 @@
       <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -548,7 +552,9 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -696,7 +702,9 @@
       <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -813,20 +821,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1010,14 +1018,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1029,6 +1029,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
